--- a/data/trans_orig/IP74A6_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP74A6_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4846</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>543</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28417</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37571</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>69346</t>
+          <t>69264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>75648</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>446</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5769</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>112531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
